--- a/MASTER_MS5673.xlsx
+++ b/MASTER_MS5673.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer_CA\★ Strim---MS Helper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CB3C45-3F23-4EEB-B7F5-23A17A730F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4636FE8-08A6-47FB-BD18-A5EFB8FB15DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2265" windowWidth="24975" windowHeight="12270" tabRatio="773" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
+    <workbookView xWindow="10050" yWindow="2220" windowWidth="18300" windowHeight="12825" tabRatio="773" activeTab="2" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER" sheetId="3" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10170" uniqueCount="4497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10200" uniqueCount="4514">
   <si>
     <t>무역거래처상호</t>
   </si>
@@ -15890,12 +15890,74 @@
   <si>
     <t>MSF-064244</t>
   </si>
+  <si>
+    <t>3NT6JRK0000</t>
+  </si>
+  <si>
+    <t>T6J RAIL R/L KIT KSW U661-903CPZZBZI</t>
+  </si>
+  <si>
+    <t>Rittal, DK7548 1945mm Long Earth Rails DK Ground Rail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rittal, DK ESD Connection Point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-079742</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOLEX-CBL,PWR,490MM,RISER 4,12 POS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>•	The products operate under DC and at ≤ 30V (24V)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>•	They are used for internal system power distribution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-067201</t>
+  </si>
+  <si>
+    <t>MSF-067201 (10129500-3CB0563LF)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCI-CBL EMASSY,MB TO PSU,68MM, VOLT:DC12V</t>
+  </si>
+  <si>
+    <t>FCI-CBL EMASSY,MB TO PSU,68MM, VOLT:DC12V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-067251 (L5QWH012-SD-R)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LUXSHARE ICT - CBL,ASSY,ASSY,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-067251</t>
+  </si>
+  <si>
+    <t>MSF-073484 (L5QWH005-SD-R)</t>
+  </si>
+  <si>
+    <t>LUXSHARE PRECISION LIMITED-CBL VOLT:5V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16075,6 +16137,12 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -16171,7 +16239,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -16309,7 +16377,13 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -16318,7 +16392,27 @@
     <cellStyle name="표준 2" xfId="1" xr:uid="{04AB7DDF-CEE2-4E84-BB25-B76053D24319}"/>
     <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="68">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -17617,12 +17711,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}">
-  <dimension ref="A1:N1151"/>
+  <dimension ref="A1:N1154"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.625" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="94.625" customWidth="1"/>
     <col min="5" max="5" width="28.375" customWidth="1"/>
     <col min="6" max="6" width="34.625" customWidth="1"/>
@@ -37518,45 +37612,78 @@
         <v>251</v>
       </c>
     </row>
+    <row r="1152" spans="1:14">
+      <c r="B1152" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>4506</v>
+      </c>
+      <c r="D1152" t="s">
+        <v>4508</v>
+      </c>
+    </row>
+    <row r="1153" spans="2:4">
+      <c r="B1153" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>4509</v>
+      </c>
+      <c r="D1153" t="s">
+        <v>4510</v>
+      </c>
+    </row>
+    <row r="1154" spans="2:4">
+      <c r="B1154" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>4512</v>
+      </c>
+      <c r="D1154" t="s">
+        <v>4513</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1149" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C995">
-    <cfRule type="duplicateValues" dxfId="65" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C996">
-    <cfRule type="duplicateValues" dxfId="64" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C2:C992 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="63" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="62" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1118">
-    <cfRule type="duplicateValues" dxfId="61" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1127">
-    <cfRule type="duplicateValues" dxfId="60" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1137">
-    <cfRule type="duplicateValues" dxfId="59" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709">
-    <cfRule type="duplicateValues" dxfId="58" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E769">
-    <cfRule type="duplicateValues" dxfId="56" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E788">
-    <cfRule type="duplicateValues" dxfId="54" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E832">
-    <cfRule type="duplicateValues" dxfId="52" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -37757,10 +37884,10 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40973,7 +41100,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB924F-9221-4917-B11B-3326F8C1F68D}">
-  <dimension ref="A1:N306"/>
+  <dimension ref="A1:N309"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
@@ -47172,90 +47299,136 @@
       <c r="D306" t="s">
         <v>4495</v>
       </c>
-      <c r="E306" s="47" t="s">
+      <c r="E306" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="307" spans="2:5">
+      <c r="B307" t="s">
+        <v>107</v>
+      </c>
+      <c r="C307" t="s">
+        <v>4505</v>
+      </c>
+      <c r="D307" t="s">
+        <v>4506</v>
+      </c>
+      <c r="E307" t="s">
+        <v>4507</v>
+      </c>
+    </row>
+    <row r="308" spans="2:5">
+      <c r="B308" t="s">
+        <v>107</v>
+      </c>
+      <c r="C308" t="s">
+        <v>4511</v>
+      </c>
+      <c r="D308" t="s">
+        <v>4509</v>
+      </c>
+      <c r="E308" t="s">
+        <v>4510</v>
+      </c>
+    </row>
+    <row r="309" spans="2:5">
+      <c r="B309" t="s">
+        <v>107</v>
+      </c>
+      <c r="C309" t="s">
+        <v>3689</v>
+      </c>
+      <c r="D309" t="s">
+        <v>4512</v>
+      </c>
+      <c r="E309" t="s">
+        <v>4513</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D2:D265">
-    <cfRule type="duplicateValues" dxfId="50" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D259:D265">
-    <cfRule type="duplicateValues" dxfId="49" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D279">
+    <cfRule type="duplicateValues" dxfId="50" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D281">
     <cfRule type="duplicateValues" dxfId="48" priority="34"/>
     <cfRule type="duplicateValues" dxfId="47" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D281">
+  <conditionalFormatting sqref="D286">
     <cfRule type="duplicateValues" dxfId="46" priority="32"/>
     <cfRule type="duplicateValues" dxfId="45" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D286">
+  <conditionalFormatting sqref="D287:D288">
     <cfRule type="duplicateValues" dxfId="44" priority="30"/>
     <cfRule type="duplicateValues" dxfId="43" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D287:D288">
+  <conditionalFormatting sqref="D290">
     <cfRule type="duplicateValues" dxfId="42" priority="28"/>
     <cfRule type="duplicateValues" dxfId="41" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D290">
+  <conditionalFormatting sqref="D292">
     <cfRule type="duplicateValues" dxfId="40" priority="26"/>
     <cfRule type="duplicateValues" dxfId="39" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D292">
+  <conditionalFormatting sqref="D293">
     <cfRule type="duplicateValues" dxfId="38" priority="24"/>
     <cfRule type="duplicateValues" dxfId="37" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D293">
+  <conditionalFormatting sqref="D294">
     <cfRule type="duplicateValues" dxfId="36" priority="22"/>
     <cfRule type="duplicateValues" dxfId="35" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D294">
+  <conditionalFormatting sqref="D295">
     <cfRule type="duplicateValues" dxfId="34" priority="20"/>
     <cfRule type="duplicateValues" dxfId="33" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D295">
+  <conditionalFormatting sqref="D296">
     <cfRule type="duplicateValues" dxfId="32" priority="18"/>
     <cfRule type="duplicateValues" dxfId="31" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D296">
+  <conditionalFormatting sqref="D298">
     <cfRule type="duplicateValues" dxfId="30" priority="16"/>
     <cfRule type="duplicateValues" dxfId="29" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D298">
+  <conditionalFormatting sqref="D299">
     <cfRule type="duplicateValues" dxfId="28" priority="14"/>
     <cfRule type="duplicateValues" dxfId="27" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D299">
+  <conditionalFormatting sqref="D300">
     <cfRule type="duplicateValues" dxfId="26" priority="12"/>
     <cfRule type="duplicateValues" dxfId="25" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D300">
-    <cfRule type="duplicateValues" dxfId="24" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D301">
-    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D302">
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D303">
     <cfRule type="duplicateValues" dxfId="21" priority="7"/>
     <cfRule type="duplicateValues" dxfId="20" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D303">
+  <conditionalFormatting sqref="D304">
     <cfRule type="duplicateValues" dxfId="19" priority="5"/>
     <cfRule type="duplicateValues" dxfId="18" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D304">
+  <conditionalFormatting sqref="D306">
     <cfRule type="duplicateValues" dxfId="17" priority="3"/>
     <cfRule type="duplicateValues" dxfId="16" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D306">
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
+  <conditionalFormatting sqref="D308">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D306">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+  <conditionalFormatting sqref="D308">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -47266,7 +47439,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:N203"/>
+  <dimension ref="A1:N207"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="17.125" style="12" customWidth="1"/>
@@ -50694,39 +50867,92 @@
         <v>4490</v>
       </c>
     </row>
+    <row r="204" spans="1:6" ht="17.25" thickBot="1">
+      <c r="A204" s="47" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B204" s="48" t="s">
+        <v>4497</v>
+      </c>
+      <c r="C204" s="42" t="s">
+        <v>4498</v>
+      </c>
+      <c r="D204">
+        <v>9403990000</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="B205" s="49">
+        <v>7548000</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>4499</v>
+      </c>
+      <c r="D205">
+        <v>8536909090</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="B206" s="49">
+        <v>7752950</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D206">
+        <v>8536909090</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="12" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B207" s="12">
+        <v>367680894</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>4502</v>
+      </c>
+      <c r="E207" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F207" t="s">
+        <v>4504</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N184" xr:uid="{F3672AAC-5183-4455-9D0B-72863BBDB2E9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A32">
-    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54:B77 B1:B52 B79:B86 B95:B144 A145:A146 B147:B198 B204:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  <conditionalFormatting sqref="B54:B77 B1:B52 B79:B86 B95:B144 A145:A146 B147:B198 B207:B1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:B94">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="G13" r:id="rId1" xr:uid="{E760DB93-B415-4120-9C80-185345A25C5F}"/>
@@ -52492,7 +52718,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1154:A1048576 A1:A170">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
